--- a/Employee_Reports_wi48/Christian Merck Morada Martija Q0624.xlsx
+++ b/Employee_Reports_wi48/Christian Merck Morada Martija Q0624.xlsx
@@ -560,11 +560,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -805,11 +805,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -854,11 +854,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1099,11 +1099,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1148,11 +1148,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1197,11 +1197,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1246,11 +1246,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1296,11 +1296,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1345,11 +1345,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1394,11 +1394,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1443,11 +1443,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
